--- a/data/fmsForecastOutput/File1/RPT_RPT4414865920010NC_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT4414865920010NC_fmsForecastOutput.xlsx
@@ -1875,49 +1875,49 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>398.6702681982124</v>
+        <v>388.280701493434</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>470.0380449862478</v>
+        <v>446.3979204036813</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>516.2316758604553</v>
+        <v>479.4752860266237</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>548.3039295407074</v>
+        <v>499.4639578156492</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>541.4867391151527</v>
+        <v>484.397537603008</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>398.6702681982124</v>
+        <v>388.280701493434</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>470.0380449862478</v>
+        <v>446.3979204036813</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>516.2316758604553</v>
+        <v>479.4752860266237</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>548.3039295407074</v>
+        <v>499.4639578156492</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>541.4867391151527</v>
+        <v>484.397537603008</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>27820.68847244128</v>
+        <v>27095.66601224223</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>26808.57955579338</v>
+        <v>25460.2670790892</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>26688.72125777444</v>
+        <v>24788.44839853517</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>24426.91574912349</v>
+        <v>22251.09717434708</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>24358.63224768841</v>
+        <v>21790.49019637812</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,49 +1925,49 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>403.4211358660966</v>
+        <v>392.9077589339739</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>475.6393870695015</v>
+        <v>451.7175482170155</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>522.3834974875543</v>
+        <v>485.1890896775167</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>554.8379493029579</v>
+        <v>505.415962160453</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>547.9395198882881</v>
+        <v>490.1699986651324</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>403.4211358660966</v>
+        <v>392.9077589339739</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>475.6393870695015</v>
+        <v>451.7175482170155</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>522.3834974875543</v>
+        <v>485.1890896775167</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>554.8379493029579</v>
+        <v>505.415962160453</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>547.9395198882881</v>
+        <v>490.1699986651324</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>27820.68847244128</v>
+        <v>27095.66601224223</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>26808.57955579338</v>
+        <v>25460.2670790892</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>26688.72125777444</v>
+        <v>24788.44839853517</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>24426.91574912349</v>
+        <v>22251.09717434708</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>24358.63224768841</v>
+        <v>21790.49019637812</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2022,49 +2022,49 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>1075.101141749012</v>
+        <v>1047.616541461619</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>1235.267532800022</v>
+        <v>1175.548253853152</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>1321.241898517294</v>
+        <v>1230.616589205168</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>1472.238865285247</v>
+        <v>1345.438078802381</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>1554.193660288991</v>
+        <v>1395.085863474005</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>1075.101141749012</v>
+        <v>1047.616541461619</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>1235.267532800022</v>
+        <v>1175.548253853152</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>1321.241898517294</v>
+        <v>1230.616589205168</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>1472.238865285247</v>
+        <v>1345.438078802381</v>
       </c>
       <c r="L9" s="157" t="n">
-        <v>1554.193660288991</v>
+        <v>1395.085863474005</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>26007.55624025287</v>
+        <v>25342.68178336935</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>26728.72446719888</v>
+        <v>25436.51843897724</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>28738.04867231166</v>
+        <v>26766.87703986658</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>30831.84816070143</v>
+        <v>28176.36698323653</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>33102.1682705018</v>
+        <v>29713.39298599887</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2072,49 +2072,49 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>1077.495576363152</v>
+        <v>1049.949763157525</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>1238.01868543432</v>
+        <v>1178.166401411845</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>1324.184530807978</v>
+        <v>1233.35738339048</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>1475.517793715727</v>
+        <v>1348.434600136017</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>1557.655116102552</v>
+        <v>1398.192958938312</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>1077.495576363152</v>
+        <v>1049.949763157525</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>1238.01868543432</v>
+        <v>1178.166401411845</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>1324.184530807978</v>
+        <v>1233.35738339048</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>1475.517793715727</v>
+        <v>1348.434600136017</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>1557.655116102552</v>
+        <v>1398.192958938312</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>26007.55624025287</v>
+        <v>25342.68178336935</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>26728.72446719888</v>
+        <v>25436.51843897724</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>28738.04867231166</v>
+        <v>26766.87703986658</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>30831.84816070143</v>
+        <v>28176.36698323653</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>33102.1682705018</v>
+        <v>29713.39298599887</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2170,49 +2170,49 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>572.7962582674036</v>
+        <v>558.0061093830845</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>680.5048662816215</v>
+        <v>646.9416205242894</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>754.6200758657409</v>
+        <v>701.9114345411623</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>843.7469337014941</v>
+        <v>769.9777419331344</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>866.8966064284836</v>
+        <v>777.0260968528866</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>572.7962582674036</v>
+        <v>558.0061093830845</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>680.5048662816215</v>
+        <v>646.9416205242894</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>754.6200758657409</v>
+        <v>701.9114345411623</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>843.7469337014941</v>
+        <v>769.9777419331344</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>866.8966064284836</v>
+        <v>777.0260968528866</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>53828.24471269416</v>
+        <v>52438.34779561157</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>53537.30402299226</v>
+        <v>50896.78551806644</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>55426.7699300861</v>
+        <v>51555.32543840175</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>55258.76390982492</v>
+        <v>50427.46415758361</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>57460.80051819021</v>
+        <v>51503.88318237699</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,49 +2220,49 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>578.183197173142</v>
+        <v>563.2539523584696</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>686.7880683345558</v>
+        <v>652.9149281663315</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>761.4327255641889</v>
+        <v>708.2482348408072</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>851.170271004584</v>
+        <v>776.7520533598628</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>874.510460624344</v>
+        <v>783.8506285951323</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>578.183197173142</v>
+        <v>563.2539523584696</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>686.7880683345558</v>
+        <v>652.9149281663315</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>761.4327255641889</v>
+        <v>708.2482348408072</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>851.170271004584</v>
+        <v>776.7520533598628</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>874.510460624344</v>
+        <v>783.8506285951323</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>53828.24471269416</v>
+        <v>52438.34779561157</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>53537.30402299226</v>
+        <v>50896.78551806644</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>55426.7699300861</v>
+        <v>51555.32543840175</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>55258.76390982492</v>
+        <v>50427.46415758361</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>57460.80051819021</v>
+        <v>51503.88318237699</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>925.4686167005005</v>
+        <v>903.5969101085145</v>
       </c>
       <c r="D11" s="156" t="n">
-        <v>987.1985745216111</v>
+        <v>942.1487575740057</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>1056.927784154938</v>
+        <v>985.4428062150025</v>
       </c>
       <c r="F11" s="156" t="n">
-        <v>1132.244368632587</v>
+        <v>1034.720722271147</v>
       </c>
       <c r="G11" s="157" t="n">
-        <v>1191.55148271664</v>
+        <v>1069.861519670341</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>925.4686167005005</v>
+        <v>903.5969101085145</v>
       </c>
       <c r="I11" s="156" t="n">
-        <v>987.1985745216111</v>
+        <v>942.1487575740057</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>1056.927784154938</v>
+        <v>985.4428062150025</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>1132.244368632587</v>
+        <v>1034.720722271147</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>1191.55148271664</v>
+        <v>1069.861519670341</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>55153.70643224254</v>
+        <v>53850.25252491581</v>
       </c>
       <c r="N11" s="159" t="n">
-        <v>65030.68546129684</v>
+        <v>62063.07534554236</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>76273.81772263565</v>
+        <v>71115.06207344362</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>89831.31637886722</v>
+        <v>82093.87226042518</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>95920.19594081001</v>
+        <v>86124.12311580834</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2368,49 +2368,49 @@
         </is>
       </c>
       <c r="T11" s="155" t="n">
-        <v>1014.38373413722</v>
+        <v>990.4106863165044</v>
       </c>
       <c r="U11" s="156" t="n">
-        <v>1082.044445686746</v>
+        <v>1032.666432523606</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>1158.472943390392</v>
+        <v>1080.119990573954</v>
       </c>
       <c r="W11" s="156" t="n">
-        <v>1241.025627323945</v>
+        <v>1134.132320757279</v>
       </c>
       <c r="X11" s="157" t="n">
-        <v>1306.030718539213</v>
+        <v>1172.649297608899</v>
       </c>
       <c r="Y11" s="155" t="n">
-        <v>1014.38373413722</v>
+        <v>990.4106863165044</v>
       </c>
       <c r="Z11" s="156" t="n">
-        <v>1082.044445686746</v>
+        <v>1032.666432523606</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>1158.472943390392</v>
+        <v>1080.119990573954</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>1241.025627323945</v>
+        <v>1134.132320757279</v>
       </c>
       <c r="AC11" s="157" t="n">
-        <v>1306.030718539213</v>
+        <v>1172.649297608899</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>55153.70643224254</v>
+        <v>53850.25252491581</v>
       </c>
       <c r="AE11" s="159" t="n">
-        <v>65030.68546129684</v>
+        <v>62063.07534554236</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>76273.81772263565</v>
+        <v>71115.06207344362</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>89831.31637886722</v>
+        <v>82093.87226042518</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>95920.19594081001</v>
+        <v>86124.12311580834</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2461,49 +2461,49 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>709.6567859565014</v>
+        <v>692.1185177439817</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>820.2735715841384</v>
+        <v>781.4755813879882</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>904.4407718154124</v>
+        <v>842.4267646600458</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>1001.787007793743</v>
+        <v>915.005028702653</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>1044.946479498633</v>
+        <v>937.625285933951</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>709.6567859565014</v>
+        <v>692.1185177439817</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>820.2735715841384</v>
+        <v>781.4755813879882</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>904.4407718154124</v>
+        <v>842.4267646600458</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>1001.787007793743</v>
+        <v>915.005028702653</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>1044.946479498633</v>
+        <v>937.625285933951</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>108981.9511449367</v>
+        <v>106288.6003205274</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>118567.9894842891</v>
+        <v>112959.8608636088</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>131700.5876527217</v>
+        <v>122670.3875118454</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>145090.0802886921</v>
+        <v>132521.3364180088</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>153380.9964590002</v>
+        <v>137628.0062981853</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2511,49 +2511,49 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>739.0080736633288</v>
+        <v>720.7444255680656</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>858.8585157415513</v>
+        <v>818.2355023616758</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>949.9965648025516</v>
+        <v>884.8589730407521</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>1056.694040429</v>
+        <v>965.1556201772282</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>1102.268486859472</v>
+        <v>989.0600384274982</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>739.0080736633288</v>
+        <v>720.7444255680656</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>858.8585157415513</v>
+        <v>818.2355023616758</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>949.9965648025516</v>
+        <v>884.8589730407521</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>1056.694040429</v>
+        <v>965.1556201772282</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>1102.268486859472</v>
+        <v>989.0600384274982</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>108981.9511449367</v>
+        <v>106288.6003205274</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>118567.9894842891</v>
+        <v>112959.8608636088</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>131700.5876527217</v>
+        <v>122670.3875118454</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>145090.0802886921</v>
+        <v>132521.3364180088</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>153380.9964590002</v>
+        <v>137628.0062981853</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2603,49 +2603,49 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>358.4725784127436</v>
+        <v>349.652275747975</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>392.3432622461778</v>
+        <v>373.7080289117015</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>433.9337426927559</v>
+        <v>403.8005396589225</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>470.3068887369909</v>
+        <v>431.3264507172673</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>512.7856709876889</v>
+        <v>464.3585334561569</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>358.4725784127436</v>
+        <v>349.652275747975</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>392.3432622461778</v>
+        <v>373.7080289117015</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>433.9337426927559</v>
+        <v>403.8005396589225</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>470.3068887369909</v>
+        <v>431.3264507172673</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>512.7856709876889</v>
+        <v>464.3585334561569</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>1551.835907006688</v>
+        <v>1513.652617097984</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>1742.588954330176</v>
+        <v>1659.820738599615</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>1985.88386678127</v>
+        <v>1847.980228801902</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>2195.99391004991</v>
+        <v>2013.983383407887</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>2442.896018495505</v>
+        <v>2212.190544149764</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2653,49 +2653,49 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>77.44777928670388</v>
+        <v>75.54215834061191</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>84.7655196210878</v>
+        <v>80.73938896240466</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>93.75111724843492</v>
+        <v>87.24085733371781</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>101.6095129987326</v>
+        <v>93.18781342657012</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>110.7870276825254</v>
+        <v>100.3243745121327</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>77.44777928670388</v>
+        <v>75.54215834061191</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>84.7655196210878</v>
+        <v>80.73938896240466</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>93.75111724843492</v>
+        <v>87.24085733371781</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>101.6095129987326</v>
+        <v>93.18781342657012</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>110.7870276825254</v>
+        <v>100.3243745121327</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>1551.835907006688</v>
+        <v>1513.652617097984</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>1742.588954330176</v>
+        <v>1659.820738599615</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>1985.88386678127</v>
+        <v>1847.980228801902</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>2195.99391004991</v>
+        <v>2013.983383407887</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>2442.896018495505</v>
+        <v>2212.190544149764</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2746,49 +2746,49 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>700.0285759661915</v>
+        <v>682.7293230658044</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>807.5165461689761</v>
+        <v>769.3196276803247</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>890.1040500242384</v>
+        <v>829.0614762181706</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>985.1875447021812</v>
+        <v>899.8985281665717</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>1028.217747070664</v>
+        <v>922.7479166451308</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>700.0285759661915</v>
+        <v>682.7293230658044</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>807.5165461689761</v>
+        <v>769.3196276803247</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>890.1040500242384</v>
+        <v>829.0614762181706</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>985.1875447021812</v>
+        <v>899.8985281665717</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>1028.217747070664</v>
+        <v>922.7479166451308</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>110533.7870519434</v>
+        <v>107802.2529376254</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>120310.5784386193</v>
+        <v>114619.6816022084</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>133686.471519503</v>
+        <v>124518.3677406473</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>147286.074198742</v>
+        <v>134535.3198014167</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>155823.8924774957</v>
+        <v>139840.1968423351</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,49 +2796,49 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>659.8725840068612</v>
+        <v>643.5656743967626</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>758.5272606822489</v>
+        <v>722.6476194722258</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>836.5065721882399</v>
+        <v>779.1396675317889</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>926.8069033239325</v>
+        <v>846.5719777729732</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>966.6453498869624</v>
+        <v>867.4913317573746</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>659.8725840068612</v>
+        <v>643.5656743967626</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>758.5272606822489</v>
+        <v>722.6476194722258</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>836.5065721882399</v>
+        <v>779.1396675317889</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>926.8069033239325</v>
+        <v>846.5719777729732</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>966.6453498869624</v>
+        <v>867.4913317573746</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>110533.7870519434</v>
+        <v>107802.2529376254</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>120310.5784386193</v>
+        <v>114619.6816022084</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>133686.471519503</v>
+        <v>124518.3677406473</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>147286.074198742</v>
+        <v>134535.3198014167</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>155823.8924774957</v>
+        <v>139840.1968423351</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>4.669278640479308</v>
       </c>
       <c r="G24" s="81" t="n">
-        <v>4.763970907748228</v>
+        <v>4.763970907748229</v>
       </c>
       <c r="H24" s="79" t="n">
         <v>0</v>
@@ -3882,7 +3882,7 @@
         <v>4.669278640479308</v>
       </c>
       <c r="Q24" s="81" t="n">
-        <v>4.763970907748228</v>
+        <v>4.763970907748229</v>
       </c>
       <c r="S24" s="32" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>20.0371904953136</v>
       </c>
       <c r="U24" s="80" t="n">
-        <v>20.55775699977727</v>
+        <v>20.55775699977728</v>
       </c>
       <c r="V24" s="80" t="n">
         <v>21.18250880700222</v>
@@ -3902,7 +3902,7 @@
         <v>21.61208970736137</v>
       </c>
       <c r="X24" s="81" t="n">
-        <v>22.05037963014894</v>
+        <v>22.05037963014895</v>
       </c>
       <c r="Y24" s="79" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>20.0371904953136</v>
       </c>
       <c r="AE24" s="80" t="n">
-        <v>20.55775699977727</v>
+        <v>20.55775699977728</v>
       </c>
       <c r="AF24" s="80" t="n">
         <v>21.18250880700222</v>
@@ -3932,7 +3932,7 @@
         <v>21.61208970736137</v>
       </c>
       <c r="AH24" s="81" t="n">
-        <v>22.05037963014894</v>
+        <v>22.05037963014895</v>
       </c>
     </row>
     <row r="25" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -4408,49 +4408,49 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>405.8570401836623</v>
+        <v>395.1696723324924</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>490.9636863282959</v>
+        <v>466.1334092224325</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>543.4302890512533</v>
+        <v>504.6431985010564</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>584.8282025319799</v>
+        <v>532.6729416795874</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>578.9790234911328</v>
+        <v>517.8532145136863</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>405.8570401836623</v>
+        <v>395.1696723324924</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>490.9636863282959</v>
+        <v>466.1334092224325</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>543.4302890512533</v>
+        <v>504.6431985010564</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>584.8282025319799</v>
+        <v>532.6729416795874</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>578.9790234911328</v>
+        <v>517.8532145136863</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>28322.20805009452</v>
+        <v>27576.4039224841</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>28002.07171383925</v>
+        <v>26585.87899011109</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>28094.86551429901</v>
+        <v>26089.60722330238</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>26054.0704913905</v>
+        <v>23730.55593299199</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>26045.21236363478</v>
+        <v>23295.48463409304</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4458,49 +4458,49 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>410.6935510644614</v>
+        <v>399.8788241538653</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>496.8143947696956</v>
+        <v>471.6882206027847</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>549.9062306901191</v>
+        <v>510.6569227409196</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>591.7974741840476</v>
+        <v>539.0206903281627</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>585.8785917371391</v>
+        <v>524.0243596674549</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>410.6935510644614</v>
+        <v>399.8788241538653</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>496.8143947696956</v>
+        <v>471.6882206027847</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>549.9062306901191</v>
+        <v>510.6569227409196</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>591.7974741840476</v>
+        <v>539.0206903281627</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>585.8785917371391</v>
+        <v>524.0243596674549</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>28322.20805009452</v>
+        <v>27576.4039224841</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>28002.07171383925</v>
+        <v>26585.87899011109</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>28094.86551429901</v>
+        <v>26089.60722330238</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>26054.0704913905</v>
+        <v>23730.55593299199</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>26045.21236363478</v>
+        <v>23295.48463409304</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4510,49 +4510,49 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>1088.422091931164</v>
+        <v>1059.944084006551</v>
       </c>
       <c r="D36" s="156" t="n">
-        <v>1289.442759230059</v>
+        <v>1226.620045327102</v>
       </c>
       <c r="E36" s="156" t="n">
-        <v>1388.989011114385</v>
+        <v>1293.129650021884</v>
       </c>
       <c r="F36" s="156" t="n">
-        <v>1567.225421588523</v>
+        <v>1431.339296310296</v>
       </c>
       <c r="G36" s="157" t="n">
-        <v>1658.548376232081</v>
+        <v>1487.598204791289</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>1088.422091931164</v>
+        <v>1059.944084006551</v>
       </c>
       <c r="I36" s="156" t="n">
-        <v>1289.442759230059</v>
+        <v>1226.620045327102</v>
       </c>
       <c r="J36" s="156" t="n">
-        <v>1388.989011114385</v>
+        <v>1293.129650021884</v>
       </c>
       <c r="K36" s="156" t="n">
-        <v>1567.225421588523</v>
+        <v>1431.339296310296</v>
       </c>
       <c r="L36" s="157" t="n">
-        <v>1658.548376232081</v>
+        <v>1487.598204791289</v>
       </c>
       <c r="M36" s="158" t="n">
-        <v>26329.80067622504</v>
+        <v>25640.89489429568</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>27900.96826196152</v>
+        <v>26541.61009410976</v>
       </c>
       <c r="O36" s="159" t="n">
-        <v>30211.6015632763</v>
+        <v>28126.58519506662</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>32821.07093582704</v>
+        <v>29975.32322428799</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>35324.77891113863</v>
+        <v>31683.77748030535</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4560,49 +4560,49 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>1090.8461945858</v>
+        <v>1062.304761253782</v>
       </c>
       <c r="U36" s="156" t="n">
-        <v>1292.314569384246</v>
+        <v>1229.351938523822</v>
       </c>
       <c r="V36" s="156" t="n">
-        <v>1392.082527842925</v>
+        <v>1296.009671514137</v>
       </c>
       <c r="W36" s="156" t="n">
-        <v>1570.715901369343</v>
+        <v>1434.527134386711</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>1662.242247894068</v>
+        <v>1490.911341104856</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>1090.8461945858</v>
+        <v>1062.304761253782</v>
       </c>
       <c r="Z36" s="156" t="n">
-        <v>1292.314569384246</v>
+        <v>1229.351938523822</v>
       </c>
       <c r="AA36" s="156" t="n">
-        <v>1392.082527842925</v>
+        <v>1296.009671514137</v>
       </c>
       <c r="AB36" s="156" t="n">
-        <v>1570.715901369343</v>
+        <v>1434.527134386711</v>
       </c>
       <c r="AC36" s="157" t="n">
-        <v>1662.242247894068</v>
+        <v>1490.911341104856</v>
       </c>
       <c r="AD36" s="158" t="n">
-        <v>26329.80067622504</v>
+        <v>25640.89489429568</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>27900.96826196152</v>
+        <v>26541.61009410976</v>
       </c>
       <c r="AF36" s="159" t="n">
-        <v>30211.6015632763</v>
+        <v>28126.58519506662</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>32821.07093582704</v>
+        <v>29975.32322428799</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>35324.77891113863</v>
+        <v>31683.77748030535</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4612,49 +4612,49 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>581.5620827377805</v>
+        <v>566.2950705535666</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>710.5753910792876</v>
+        <v>675.2957683414435</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>793.8263525917658</v>
+        <v>738.1383993241417</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>898.965458791675</v>
+        <v>820.0359120346008</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>925.8735815176274</v>
+        <v>829.4582623474943</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>581.5620827377805</v>
+        <v>566.2950705535666</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>710.5753910792876</v>
+        <v>675.2957683414435</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>793.8263525917658</v>
+        <v>738.1383993241417</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>898.965458791675</v>
+        <v>820.0359120346008</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>925.8735815176274</v>
+        <v>829.4582623474943</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>54652.00872631956</v>
+        <v>53217.29881677978</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>55903.03997580076</v>
+        <v>53127.48908422085</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>58306.46707757532</v>
+        <v>54216.192418369</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>58875.14142721755</v>
+        <v>53705.87915727997</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>61369.99127477341</v>
+        <v>54979.26211439839</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4662,49 +4662,49 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>587.0314610103947</v>
+        <v>571.6208681712401</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>717.1362387340437</v>
+        <v>681.5308740228551</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>800.9929534211965</v>
+        <v>744.802253764801</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>906.8746120672453</v>
+        <v>827.2506383139303</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>934.0054237710159</v>
+        <v>836.7432998297428</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>587.0314610103947</v>
+        <v>571.6208681712401</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>717.1362387340437</v>
+        <v>681.5308740228551</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>800.9929534211965</v>
+        <v>744.802253764801</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>906.8746120672453</v>
+        <v>827.2506383139303</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>934.0054237710159</v>
+        <v>836.7432998297428</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>54652.00872631956</v>
+        <v>53217.29881677978</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>55903.03997580076</v>
+        <v>53127.48908422085</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>58306.46707757532</v>
+        <v>54216.192418369</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>58875.14142721755</v>
+        <v>53705.87915727997</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>61369.99127477341</v>
+        <v>54979.26211439839</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4714,49 +4714,49 @@
         </is>
       </c>
       <c r="C38" s="155" t="n">
-        <v>946.2000887448385</v>
+        <v>923.7973521908262</v>
       </c>
       <c r="D38" s="156" t="n">
-        <v>1032.705485420063</v>
+        <v>985.4681696314484</v>
       </c>
       <c r="E38" s="156" t="n">
-        <v>1112.37738860219</v>
+        <v>1036.917124287372</v>
       </c>
       <c r="F38" s="156" t="n">
-        <v>1205.922877818226</v>
+        <v>1101.588663297958</v>
       </c>
       <c r="G38" s="157" t="n">
-        <v>1270.521214318287</v>
+        <v>1139.815522846281</v>
       </c>
       <c r="H38" s="155" t="n">
-        <v>946.2000887448385</v>
+        <v>923.7973521908262</v>
       </c>
       <c r="I38" s="156" t="n">
-        <v>1032.705485420063</v>
+        <v>985.4681696314484</v>
       </c>
       <c r="J38" s="156" t="n">
-        <v>1112.37738860219</v>
+        <v>1036.917124287372</v>
       </c>
       <c r="K38" s="156" t="n">
-        <v>1205.922877818226</v>
+        <v>1101.588663297958</v>
       </c>
       <c r="L38" s="157" t="n">
-        <v>1270.521214318287</v>
+        <v>1139.815522846281</v>
       </c>
       <c r="M38" s="158" t="n">
-        <v>56389.2075636782</v>
+        <v>55054.1066938248</v>
       </c>
       <c r="N38" s="159" t="n">
-        <v>68028.40616848743</v>
+        <v>64916.69682817164</v>
       </c>
       <c r="O38" s="159" t="n">
-        <v>80275.37117388066</v>
+        <v>74829.73663580077</v>
       </c>
       <c r="P38" s="159" t="n">
-        <v>95676.90735934766</v>
+        <v>87399.11848853173</v>
       </c>
       <c r="Q38" s="160" t="n">
-        <v>102277.2793220108</v>
+        <v>91755.43807685556</v>
       </c>
       <c r="S38" s="32" t="inlineStr">
         <is>
@@ -4764,49 +4764,49 @@
         </is>
       </c>
       <c r="T38" s="155" t="n">
-        <v>1037.10699848893</v>
+        <v>1012.551901589404</v>
       </c>
       <c r="U38" s="156" t="n">
-        <v>1131.923468457714</v>
+        <v>1080.14779080037</v>
       </c>
       <c r="V38" s="156" t="n">
-        <v>1219.249911729058</v>
+        <v>1136.539743806185</v>
       </c>
       <c r="W38" s="156" t="n">
-        <v>1321.782856607258</v>
+        <v>1207.424651246747</v>
       </c>
       <c r="X38" s="157" t="n">
-        <v>1392.587528549137</v>
+        <v>1249.324186069672</v>
       </c>
       <c r="Y38" s="155" t="n">
-        <v>1037.10699848893</v>
+        <v>1012.551901589404</v>
       </c>
       <c r="Z38" s="156" t="n">
-        <v>1131.923468457714</v>
+        <v>1080.14779080037</v>
       </c>
       <c r="AA38" s="156" t="n">
-        <v>1219.249911729058</v>
+        <v>1136.539743806185</v>
       </c>
       <c r="AB38" s="156" t="n">
-        <v>1321.782856607258</v>
+        <v>1207.424651246747</v>
       </c>
       <c r="AC38" s="157" t="n">
-        <v>1392.587528549137</v>
+        <v>1249.324186069672</v>
       </c>
       <c r="AD38" s="158" t="n">
-        <v>56389.2075636782</v>
+        <v>55054.1066938248</v>
       </c>
       <c r="AE38" s="159" t="n">
-        <v>68028.40616848743</v>
+        <v>64916.69682817164</v>
       </c>
       <c r="AF38" s="159" t="n">
-        <v>80275.37117388066</v>
+        <v>74829.73663580077</v>
       </c>
       <c r="AG38" s="159" t="n">
-        <v>95676.90735934766</v>
+        <v>87399.11848853173</v>
       </c>
       <c r="AH38" s="160" t="n">
-        <v>102277.2793220108</v>
+        <v>91755.43807685556</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" thickTop="1">
@@ -4816,49 +4816,49 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>723.066084183625</v>
+        <v>705.0299323735171</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>857.3788794304618</v>
+        <v>816.6498091454145</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>951.6970803368714</v>
+        <v>886.2101662078517</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>1067.117987626839</v>
+        <v>974.2716600271792</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>1114.888045047875</v>
+        <v>999.6669204461994</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>723.066084183625</v>
+        <v>705.0299323735171</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>857.3788794304618</v>
+        <v>816.6498091454145</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>951.6970803368714</v>
+        <v>886.2101662078517</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>1067.117987626839</v>
+        <v>974.2716600271792</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>1114.888045047875</v>
+        <v>999.6669204461994</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>111041.2162899978</v>
+        <v>108271.4055106046</v>
       </c>
       <c r="N39" s="165" t="n">
-        <v>123931.4461442882</v>
+        <v>118044.1859123925</v>
       </c>
       <c r="O39" s="165" t="n">
-        <v>138581.838251456</v>
+        <v>129045.9290541698</v>
       </c>
       <c r="P39" s="165" t="n">
-        <v>154552.0487865652</v>
+        <v>141104.9976458117</v>
       </c>
       <c r="Q39" s="166" t="n">
-        <v>163647.2705967842</v>
+        <v>146734.7001912539</v>
       </c>
       <c r="S39" s="42" t="inlineStr">
         <is>
@@ -4866,49 +4866,49 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>752.9719782551058</v>
+        <v>734.1898541787157</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>897.7092244892217</v>
+        <v>855.064294719031</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>999.6331271509348</v>
+        <v>930.8477015036427</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>1125.605751708883</v>
+        <v>1027.670601535245</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>1176.046795260048</v>
+        <v>1054.505053974052</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>752.9719782551058</v>
+        <v>734.1898541787157</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>897.7092244892217</v>
+        <v>855.064294719031</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>999.6331271509348</v>
+        <v>930.8477015036427</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>1125.605751708883</v>
+        <v>1027.670601535245</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>1176.046795260048</v>
+        <v>1054.505053974052</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>111041.2162899978</v>
+        <v>108271.4055106046</v>
       </c>
       <c r="AE39" s="165" t="n">
-        <v>123931.4461442882</v>
+        <v>118044.1859123925</v>
       </c>
       <c r="AF39" s="165" t="n">
-        <v>138581.838251456</v>
+        <v>129045.9290541698</v>
       </c>
       <c r="AG39" s="165" t="n">
-        <v>154552.0487865652</v>
+        <v>141104.9976458117</v>
       </c>
       <c r="AH39" s="166" t="n">
-        <v>163647.2705967842</v>
+        <v>146734.7001912539</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -4918,49 +4918,49 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>320.6687990267247</v>
+        <v>311.3959104836098</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>352.2890007084519</v>
+        <v>332.1234555271661</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>387.2241012132336</v>
+        <v>354.2484841161863</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>419.7639390213697</v>
+        <v>376.3737671235042</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>453.9534616845575</v>
+        <v>399.6853179924828</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>320.6687990267247</v>
+        <v>311.3959104836098</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>352.2890007084519</v>
+        <v>332.1234555271661</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>387.2241012132336</v>
+        <v>354.2484841161863</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>419.7639390213697</v>
+        <v>376.3737671235042</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>453.9534616845575</v>
+        <v>399.6853179924828</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>1388.182490247327</v>
+        <v>1348.039945825678</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>1564.688323821328</v>
+        <v>1475.123242240022</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>1772.118689494749</v>
+        <v>1621.206834648398</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>1959.99479451594</v>
+        <v>1757.393991666511</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>2162.621084936832</v>
+        <v>1904.089227170288</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4968,49 +4968,49 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>69.28029608602078</v>
+        <v>67.27689424028608</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>76.11182114071494</v>
+        <v>71.75506755216553</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>83.65952803989616</v>
+        <v>76.53516632139826</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>90.68973991202434</v>
+        <v>81.31532005754721</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>98.07636517876243</v>
+        <v>86.35176623294382</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>69.28029608602078</v>
+        <v>67.27689424028608</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>76.11182114071494</v>
+        <v>71.75506755216553</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>83.65952803989616</v>
+        <v>76.53516632139826</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>90.68973991202434</v>
+        <v>81.31532005754721</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>98.07636517876243</v>
+        <v>86.35176623294382</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>1388.182490247327</v>
+        <v>1348.039945825678</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>1564.688323821328</v>
+        <v>1475.123242240022</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>1772.118689494749</v>
+        <v>1621.206834648398</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>1959.99479451594</v>
+        <v>1757.393991666511</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>2162.621084936832</v>
+        <v>1904.089227170288</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5020,49 +5020,49 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>712.0337954935408</v>
+        <v>694.2379008963784</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>842.3216510005188</v>
+        <v>802.2055997203179</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>934.4971416336789</v>
+        <v>870.0008724722524</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>1046.899489790889</v>
+        <v>955.5978025301367</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>1094.111246718037</v>
+        <v>980.8062085549263</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>712.0337954935408</v>
+        <v>694.2379008963784</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>842.3216510005188</v>
+        <v>802.2055997203179</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>934.4971416336789</v>
+        <v>870.0008724722524</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>1046.899489790889</v>
+        <v>955.5978025301367</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>1094.111246718037</v>
+        <v>980.8062085549263</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>112429.3987802451</v>
+        <v>109619.4454564302</v>
       </c>
       <c r="N41" s="183" t="n">
-        <v>125496.1344681095</v>
+        <v>119519.3091546325</v>
       </c>
       <c r="O41" s="183" t="n">
-        <v>140353.9569409507</v>
+        <v>130667.1358888182</v>
       </c>
       <c r="P41" s="183" t="n">
-        <v>156512.0435810811</v>
+        <v>142862.3916374782</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>165809.8916817211</v>
+        <v>148638.7894184242</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5070,49 +5070,49 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>671.1891437917922</v>
+        <v>654.4140815218908</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>791.2208580467592</v>
+        <v>753.5385113117959</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>878.2265406459055</v>
+        <v>817.6139043662639</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>984.8618970490633</v>
+        <v>898.9706020429248</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>1028.592972560638</v>
+        <v>922.0729396481853</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>671.1891437917922</v>
+        <v>654.4140815218908</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>791.2208580467592</v>
+        <v>753.5385113117959</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>878.2265406459055</v>
+        <v>817.6139043662639</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>984.8618970490633</v>
+        <v>898.9706020429248</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>1028.592972560638</v>
+        <v>922.0729396481853</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>112429.3987802451</v>
+        <v>109619.4454564302</v>
       </c>
       <c r="AE41" s="189" t="n">
-        <v>125496.1344681095</v>
+        <v>119519.3091546325</v>
       </c>
       <c r="AF41" s="189" t="n">
-        <v>140353.9569409507</v>
+        <v>130667.1358888182</v>
       </c>
       <c r="AG41" s="189" t="n">
-        <v>156512.0435810811</v>
+        <v>142862.3916374782</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>165809.8916817211</v>
+        <v>148638.7894184242</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.3021198406140173</v>
+        <v>0.3101013105104077</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.04515711930786146</v>
+        <v>0.04772309781240928</v>
       </c>
       <c r="E57" s="149" t="n">
         <v>0</v>
@@ -6349,10 +6349,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.3021198406140173</v>
+        <v>0.3101013105104077</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.04515711930786146</v>
+        <v>0.04772309781240928</v>
       </c>
       <c r="J57" s="149" t="n">
         <v>0</v>
@@ -6364,10 +6364,10 @@
         <v>0</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>21.08304189588392</v>
+        <v>21.64001843828623</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>2.57553242421191</v>
+        <v>2.721882787999247</v>
       </c>
       <c r="O57" s="152" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.3057201376441581</v>
+        <v>0.3137967209972011</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.04569524696675136</v>
+        <v>0.04829180368413867</v>
       </c>
       <c r="V57" s="149" t="n">
         <v>0</v>
@@ -6399,10 +6399,10 @@
         <v>0</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>0.3057201376441581</v>
+        <v>0.3137967209972011</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>0.04569524696675136</v>
+        <v>0.04829180368413867</v>
       </c>
       <c r="AA57" s="149" t="n">
         <v>0</v>
@@ -6414,10 +6414,10 @@
         <v>0</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>21.08304189588392</v>
+        <v>21.64001843828623</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>2.57553242421191</v>
+        <v>2.721882787999247</v>
       </c>
       <c r="AF57" s="152" t="n">
         <v>0</v>
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="C58" s="155" t="n">
-        <v>6.561303795942799</v>
+        <v>6.758487397916835</v>
       </c>
       <c r="D58" s="156" t="n">
-        <v>1.057076830950801</v>
+        <v>1.127972164136653</v>
       </c>
       <c r="E58" s="156" t="n">
         <v>0</v>
@@ -6451,10 +6451,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="155" t="n">
-        <v>6.561303795942799</v>
+        <v>6.758487397916835</v>
       </c>
       <c r="I58" s="156" t="n">
-        <v>1.057076830950801</v>
+        <v>1.127972164136653</v>
       </c>
       <c r="J58" s="156" t="n">
         <v>0</v>
@@ -6466,10 +6466,10 @@
         <v>0</v>
       </c>
       <c r="M58" s="158" t="n">
-        <v>158.7231850621592</v>
+        <v>163.4932140565034</v>
       </c>
       <c r="N58" s="159" t="n">
-        <v>22.87303325385615</v>
+        <v>24.40706679429865</v>
       </c>
       <c r="O58" s="159" t="n">
         <v>0</v>
@@ -6486,10 +6486,10 @@
         </is>
       </c>
       <c r="T58" s="155" t="n">
-        <v>6.575916944708819</v>
+        <v>6.773539708379901</v>
       </c>
       <c r="U58" s="156" t="n">
-        <v>1.059431122333765</v>
+        <v>1.130484351584619</v>
       </c>
       <c r="V58" s="156" t="n">
         <v>0</v>
@@ -6501,10 +6501,10 @@
         <v>0</v>
       </c>
       <c r="Y58" s="155" t="n">
-        <v>6.575916944708819</v>
+        <v>6.773539708379901</v>
       </c>
       <c r="Z58" s="156" t="n">
-        <v>1.059431122333765</v>
+        <v>1.130484351584619</v>
       </c>
       <c r="AA58" s="156" t="n">
         <v>0</v>
@@ -6516,10 +6516,10 @@
         <v>0</v>
       </c>
       <c r="AD58" s="158" t="n">
-        <v>158.7231850621592</v>
+        <v>163.4932140565034</v>
       </c>
       <c r="AE58" s="159" t="n">
-        <v>22.87303325385615</v>
+        <v>24.40706679429865</v>
       </c>
       <c r="AF58" s="159" t="n">
         <v>0</v>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>1.91335115169487</v>
+        <v>1.970036797966716</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.3234730082107868</v>
+        <v>0.3448321230358183</v>
       </c>
       <c r="E59" s="162" t="n">
         <v>0</v>
@@ -6553,10 +6553,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>1.91335115169487</v>
+        <v>1.970036797966716</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.3234730082107868</v>
+        <v>0.3448321230358183</v>
       </c>
       <c r="J59" s="162" t="n">
         <v>0</v>
@@ -6568,10 +6568,10 @@
         <v>0</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>179.8062269580431</v>
+        <v>185.1332324947897</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>25.44856567806806</v>
+        <v>27.12894958229789</v>
       </c>
       <c r="O59" s="165" t="n">
         <v>0</v>
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>1.93134551812209</v>
+        <v>1.988564272124463</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.3264596823257927</v>
+        <v>0.3480160090162599</v>
       </c>
       <c r="V59" s="162" t="n">
         <v>0</v>
@@ -6603,10 +6603,10 @@
         <v>0</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>1.93134551812209</v>
+        <v>1.988564272124463</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.3264596823257927</v>
+        <v>0.3480160090162599</v>
       </c>
       <c r="AA59" s="162" t="n">
         <v>0</v>
@@ -6618,10 +6618,10 @@
         <v>0</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>179.8062269580431</v>
+        <v>185.1332324947897</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>25.44856567806806</v>
+        <v>27.12894958229789</v>
       </c>
       <c r="AF59" s="165" t="n">
         <v>0</v>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>1.170842582441124</v>
+        <v>1.2055303962329</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.176057517304942</v>
+        <v>0.1876826997234879</v>
       </c>
       <c r="E61" s="162" t="n">
         <v>0</v>
@@ -6757,10 +6757,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>1.170842582441124</v>
+        <v>1.2055303962329</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.176057517304942</v>
+        <v>0.1876826997234879</v>
       </c>
       <c r="J61" s="162" t="n">
         <v>0</v>
@@ -6772,10 +6772,10 @@
         <v>0</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>179.8062269580431</v>
+        <v>185.1332324947897</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>25.44856567806806</v>
+        <v>27.12894958229789</v>
       </c>
       <c r="O61" s="165" t="n">
         <v>0</v>
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>1.219268438681355</v>
+        <v>1.255390934734573</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.1843391073854133</v>
+        <v>0.1965111281149548</v>
       </c>
       <c r="V61" s="162" t="n">
         <v>0</v>
@@ -6807,10 +6807,10 @@
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>1.219268438681355</v>
+        <v>1.255390934734573</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.1843391073854133</v>
+        <v>0.1965111281149548</v>
       </c>
       <c r="AA61" s="162" t="n">
         <v>0</v>
@@ -6822,10 +6822,10 @@
         <v>0</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>179.8062269580431</v>
+        <v>185.1332324947897</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>25.44856567806806</v>
+        <v>27.12894958229789</v>
       </c>
       <c r="AF61" s="165" t="n">
         <v>0</v>
@@ -6946,10 +6946,10 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>1.138742282919725</v>
+        <v>1.172479081409225</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.1708090687286676</v>
+        <v>0.1820876929709564</v>
       </c>
       <c r="E63" s="180" t="n">
         <v>0</v>
@@ -6961,10 +6961,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>1.138742282919725</v>
+        <v>1.172479081409225</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.1708090687286676</v>
+        <v>0.1820876929709564</v>
       </c>
       <c r="J63" s="180" t="n">
         <v>0</v>
@@ -6976,10 +6976,10 @@
         <v>0</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>179.8062269580431</v>
+        <v>185.1332324947897</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>25.44856567806806</v>
+        <v>27.12894958229789</v>
       </c>
       <c r="O63" s="183" t="n">
         <v>0</v>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>1.073420198184027</v>
+        <v>1.105221740520578</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.1604466628171486</v>
+        <v>0.1710410512434356</v>
       </c>
       <c r="V63" s="186" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>1.073420198184027</v>
+        <v>1.105221740520578</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.1604466628171486</v>
+        <v>0.1710410512434356</v>
       </c>
       <c r="AA63" s="186" t="n">
         <v>0</v>
@@ -7026,10 +7026,10 @@
         <v>0</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>179.8062269580431</v>
+        <v>185.1332324947897</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>25.44856567806806</v>
+        <v>27.12894958229789</v>
       </c>
       <c r="AF63" s="189" t="n">
         <v>0</v>
@@ -7297,49 +7297,49 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>1.840019621548196</v>
+        <v>1.888629673732478</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>1.239854376999804</v>
+        <v>1.310307048226713</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.6309997533837135</v>
+        <v>0.6798493372454784</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.3249907483602633</v>
+        <v>0.3571808177187467</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.3501278464555653</v>
+        <v>0.3959272768541202</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>1.840019621548196</v>
+        <v>1.888629673732478</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>1.239854376999804</v>
+        <v>1.310307048226713</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.6309997533837135</v>
+        <v>0.6798493372454784</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.3249907483602633</v>
+        <v>0.3571808177187467</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.3501278464555653</v>
+        <v>0.3959272768541202</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>128.4033868530686</v>
+        <v>131.7955764050009</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>70.71498798436707</v>
+        <v>74.73325004134584</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>32.62212940287412</v>
+        <v>35.14760970214451</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>14.47832342928954</v>
+        <v>15.91238959189533</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>15.75040501531567</v>
+        <v>17.81067981365151</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7347,49 +7347,49 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>1.861946738831845</v>
+        <v>1.911136066531957</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>1.254629454406993</v>
+        <v>1.325921694933515</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.6385192414567573</v>
+        <v>0.6879509552817303</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>0.3288635930690607</v>
+        <v>0.3614372645467424</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>0.3543002445450176</v>
+        <v>0.4006454568853045</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>1.861946738831845</v>
+        <v>1.911136066531957</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>1.254629454406993</v>
+        <v>1.325921694933515</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.6385192414567573</v>
+        <v>0.6879509552817303</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.3288635930690607</v>
+        <v>0.3614372645467424</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.3543002445450176</v>
+        <v>0.4006454568853045</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>128.4033868530686</v>
+        <v>131.7955764050009</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>70.71498798436707</v>
+        <v>74.73325004134584</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>32.62212940287412</v>
+        <v>35.14760970214451</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>14.47832342928954</v>
+        <v>15.91238959189533</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>15.75040501531567</v>
+        <v>17.81067981365151</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7399,49 +7399,49 @@
         </is>
       </c>
       <c r="C69" s="155" t="n">
-        <v>5.14556700413425</v>
+        <v>5.300204171933326</v>
       </c>
       <c r="D69" s="156" t="n">
-        <v>3.093108106104748</v>
+        <v>3.300554644843954</v>
       </c>
       <c r="E69" s="156" t="n">
-        <v>3.473079703178348</v>
+        <v>3.819913005419322</v>
       </c>
       <c r="F69" s="156" t="n">
-        <v>3.918512959555194</v>
+        <v>4.474202520680724</v>
       </c>
       <c r="G69" s="157" t="n">
-        <v>4.220471598372009</v>
+        <v>4.932922920770681</v>
       </c>
       <c r="H69" s="155" t="n">
-        <v>5.14556700413425</v>
+        <v>5.300204171933326</v>
       </c>
       <c r="I69" s="156" t="n">
-        <v>3.093108106104748</v>
+        <v>3.300554644843954</v>
       </c>
       <c r="J69" s="156" t="n">
-        <v>3.473079703178348</v>
+        <v>3.819913005419322</v>
       </c>
       <c r="K69" s="156" t="n">
-        <v>3.918512959555194</v>
+        <v>4.474202520680724</v>
       </c>
       <c r="L69" s="157" t="n">
-        <v>4.220471598372009</v>
+        <v>4.932922920770681</v>
       </c>
       <c r="M69" s="158" t="n">
-        <v>124.4753800840562</v>
+        <v>128.216176816748</v>
       </c>
       <c r="N69" s="159" t="n">
-        <v>66.92868720343631</v>
+        <v>71.41741634785559</v>
       </c>
       <c r="O69" s="159" t="n">
-        <v>75.5422104497019</v>
+        <v>83.08610709131239</v>
       </c>
       <c r="P69" s="159" t="n">
-        <v>82.06208885902393</v>
+        <v>93.69942338203943</v>
       </c>
       <c r="Q69" s="160" t="n">
-        <v>89.89018846223225</v>
+        <v>105.0644129885356</v>
       </c>
       <c r="S69" s="32" t="inlineStr">
         <is>
@@ -7449,49 +7449,49 @@
         </is>
       </c>
       <c r="T69" s="155" t="n">
-        <v>5.157027064277088</v>
+        <v>5.312008635567921</v>
       </c>
       <c r="U69" s="156" t="n">
-        <v>3.099996988300972</v>
+        <v>3.307905546057415</v>
       </c>
       <c r="V69" s="156" t="n">
-        <v>3.480814847283423</v>
+        <v>3.828420606767694</v>
       </c>
       <c r="W69" s="156" t="n">
-        <v>3.927240159910551</v>
+        <v>4.484167336985136</v>
       </c>
       <c r="X69" s="157" t="n">
-        <v>4.229871312399563</v>
+        <v>4.943909386073066</v>
       </c>
       <c r="Y69" s="155" t="n">
-        <v>5.157027064277088</v>
+        <v>5.312008635567921</v>
       </c>
       <c r="Z69" s="156" t="n">
-        <v>3.099996988300972</v>
+        <v>3.307905546057415</v>
       </c>
       <c r="AA69" s="156" t="n">
-        <v>3.480814847283423</v>
+        <v>3.828420606767694</v>
       </c>
       <c r="AB69" s="156" t="n">
-        <v>3.927240159910551</v>
+        <v>4.484167336985136</v>
       </c>
       <c r="AC69" s="157" t="n">
-        <v>4.229871312399563</v>
+        <v>4.943909386073066</v>
       </c>
       <c r="AD69" s="158" t="n">
-        <v>124.4753800840562</v>
+        <v>128.216176816748</v>
       </c>
       <c r="AE69" s="159" t="n">
-        <v>66.92868720343631</v>
+        <v>71.41741634785559</v>
       </c>
       <c r="AF69" s="159" t="n">
-        <v>75.5422104497019</v>
+        <v>83.08610709131239</v>
       </c>
       <c r="AG69" s="159" t="n">
-        <v>82.06208885902393</v>
+        <v>93.69942338203943</v>
       </c>
       <c r="AH69" s="160" t="n">
-        <v>89.89018846223225</v>
+        <v>105.0644129885356</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" thickTop="1">
@@ -7501,49 +7501,49 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>2.690929497515286</v>
+        <v>2.766832917288917</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>1.749568688366537</v>
+        <v>1.857699813301034</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>1.472627440647828</v>
+        <v>1.609719210574759</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>1.474077070914354</v>
+        <v>1.673664493204045</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>1.593772992386109</v>
+        <v>1.853785537343501</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>2.690929497515286</v>
+        <v>2.766832917288917</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>1.749568688366537</v>
+        <v>1.857699813301034</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>1.472627440647828</v>
+        <v>1.609719210574759</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>1.474077070914354</v>
+        <v>1.673664493204045</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>1.593772992386109</v>
+        <v>1.853785537343501</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>252.8787669371248</v>
+        <v>260.0117532217489</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>137.6436751878034</v>
+        <v>146.1506663892014</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>108.164339852576</v>
+        <v>118.2337167934569</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>96.54041228831346</v>
+        <v>109.6118129739348</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>105.6405934775479</v>
+        <v>122.8750928021871</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7551,49 +7551,49 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>2.716236703338542</v>
+        <v>2.79285396696006</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>1.765722714765438</v>
+        <v>1.874852230365217</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>1.485922203416955</v>
+        <v>1.624251626879648</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>1.48704609144773</v>
+        <v>1.68838949612732</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>1.607770919123095</v>
+        <v>1.870067124659754</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>2.716236703338542</v>
+        <v>2.79285396696006</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>1.765722714765438</v>
+        <v>1.874852230365217</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>1.485922203416955</v>
+        <v>1.624251626879648</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>1.48704609144773</v>
+        <v>1.68838949612732</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>1.607770919123095</v>
+        <v>1.870067124659754</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>252.8787669371248</v>
+        <v>260.0117532217489</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>137.6436751878034</v>
+        <v>146.1506663892014</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>108.164339852576</v>
+        <v>118.2337167934569</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>96.54041228831346</v>
+        <v>109.6118129739348</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>105.6405934775479</v>
+        <v>122.8750928021871</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7603,49 +7603,49 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>0.8604898787695601</v>
+        <v>0.8822263990504747</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>1.143804330213192</v>
+        <v>1.202577205267193</v>
       </c>
       <c r="E71" s="156" t="n">
-        <v>1.527610520250207</v>
+        <v>1.648435690767439</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>2.393468402265413</v>
+        <v>2.645991431292258</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>4.258292614547694</v>
+        <v>4.762082711455975</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>0.8604898787695601</v>
+        <v>0.8822263990504747</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>1.143804330213192</v>
+        <v>1.202577205267193</v>
       </c>
       <c r="J71" s="156" t="n">
-        <v>1.527610520250207</v>
+        <v>1.648435690767439</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>2.393468402265413</v>
+        <v>2.645991431292258</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>4.258292614547694</v>
+        <v>4.762082711455975</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>51.28127016427074</v>
+        <v>52.57666758434341</v>
       </c>
       <c r="N71" s="159" t="n">
-        <v>75.3469277074357</v>
+        <v>79.21853008808637</v>
       </c>
       <c r="O71" s="159" t="n">
-        <v>110.2409153392682</v>
+        <v>118.9603351241367</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>189.8957709512762</v>
+        <v>209.9307357891729</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>342.7936332465233</v>
+        <v>383.3488635570995</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7653,49 +7653,49 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>0.9431621134010062</v>
+        <v>0.9669869867806286</v>
       </c>
       <c r="U71" s="156" t="n">
-        <v>1.253696221207965</v>
+        <v>1.318115745962688</v>
       </c>
       <c r="V71" s="156" t="n">
-        <v>1.674376889584124</v>
+        <v>1.806810432370265</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>2.62342274131933</v>
+        <v>2.900207116842665</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>4.667411390776228</v>
+        <v>5.219603513233206</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>0.9431621134010062</v>
+        <v>0.9669869867806286</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>1.253696221207965</v>
+        <v>1.318115745962688</v>
       </c>
       <c r="AA71" s="156" t="n">
-        <v>1.674376889584124</v>
+        <v>1.806810432370265</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>2.62342274131933</v>
+        <v>2.900207116842665</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>4.667411390776228</v>
+        <v>5.219603513233206</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>51.28127016427074</v>
+        <v>52.57666758434341</v>
       </c>
       <c r="AE71" s="159" t="n">
-        <v>75.3469277074357</v>
+        <v>79.21853008808637</v>
       </c>
       <c r="AF71" s="159" t="n">
-        <v>110.2409153392682</v>
+        <v>118.9603351241367</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>189.8957709512762</v>
+        <v>209.9307357891729</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>342.7936332465233</v>
+        <v>383.3488635570995</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7705,49 +7705,49 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>1.98059616365948</v>
+        <v>2.035479193627706</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>1.473505313792023</v>
+        <v>1.559142535211561</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>1.499876508487025</v>
+        <v>1.628906713400985</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>1.977723400252419</v>
+        <v>2.2063091642877</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>3.055070558413454</v>
+        <v>3.448777575107912</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>1.98059616365948</v>
+        <v>2.035479193627706</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>1.473505313792023</v>
+        <v>1.559142535211561</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>1.499876508487025</v>
+        <v>1.628906713400985</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>1.977723400252419</v>
+        <v>2.2063091642877</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>3.055070558413454</v>
+        <v>3.448777575107912</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>304.1600371013955</v>
+        <v>312.5884208060922</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>212.9906028952391</v>
+        <v>225.3691964772878</v>
       </c>
       <c r="O72" s="165" t="n">
-        <v>218.4052551918442</v>
+        <v>237.1940519175936</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>286.4361832395897</v>
+        <v>319.5425487631076</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>448.4342267240712</v>
+        <v>506.2239563592866</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7755,49 +7755,49 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>2.062513294561363</v>
+        <v>2.119666277603663</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>1.542817702021862</v>
+        <v>1.632483222682942</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>1.575423814464572</v>
+        <v>1.710953144017009</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>2.086120616862689</v>
+        <v>2.327234958238458</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>3.222660746497811</v>
+        <v>3.637965114780842</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>2.062513294561363</v>
+        <v>2.119666277603663</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>1.542817702021862</v>
+        <v>1.632483222682942</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>1.575423814464572</v>
+        <v>1.710953144017009</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>2.086120616862689</v>
+        <v>2.327234958238458</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>3.222660746497811</v>
+        <v>3.637965114780842</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>304.1600371013955</v>
+        <v>312.5884208060922</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>212.9906028952391</v>
+        <v>225.3691964772878</v>
       </c>
       <c r="AF72" s="165" t="n">
-        <v>218.4052551918442</v>
+        <v>237.1940519175936</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>286.4361832395897</v>
+        <v>319.5425487631076</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>448.4342267240712</v>
+        <v>506.2239563592866</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7807,49 +7807,49 @@
         </is>
       </c>
       <c r="C73" s="155" t="n">
-        <v>47.2804736992541</v>
+        <v>47.53321318737323</v>
       </c>
       <c r="D73" s="156" t="n">
-        <v>58.658378389092</v>
+        <v>59.30936481997549</v>
       </c>
       <c r="E73" s="156" t="n">
-        <v>69.86823003427472</v>
+        <v>71.08009863434312</v>
       </c>
       <c r="F73" s="156" t="n">
-        <v>81.15113088855017</v>
+        <v>82.91792023036146</v>
       </c>
       <c r="G73" s="157" t="n">
-        <v>93.4566075326219</v>
+        <v>95.88324361316492</v>
       </c>
       <c r="H73" s="155" t="n">
-        <v>47.2804736992541</v>
+        <v>47.53321318737323</v>
       </c>
       <c r="I73" s="156" t="n">
-        <v>58.658378389092</v>
+        <v>59.30936481997549</v>
       </c>
       <c r="J73" s="156" t="n">
-        <v>69.86823003427472</v>
+        <v>71.08009863434312</v>
       </c>
       <c r="K73" s="156" t="n">
-        <v>81.15113088855017</v>
+        <v>82.91792023036146</v>
       </c>
       <c r="L73" s="157" t="n">
-        <v>93.4566075326219</v>
+        <v>95.88324361316492</v>
       </c>
       <c r="M73" s="158" t="n">
-        <v>204.6782409735905</v>
+        <v>205.7723559391435</v>
       </c>
       <c r="N73" s="159" t="n">
-        <v>260.5306426687525</v>
+        <v>263.4219928537459</v>
       </c>
       <c r="O73" s="159" t="n">
-        <v>319.7497156239126</v>
+        <v>325.2957934343184</v>
       </c>
       <c r="P73" s="159" t="n">
-        <v>378.9172421086479</v>
+        <v>387.1668738445939</v>
       </c>
       <c r="Q73" s="160" t="n">
-        <v>445.2245594222547</v>
+        <v>456.7849831136539</v>
       </c>
       <c r="S73" s="32" t="inlineStr">
         <is>
@@ -7857,49 +7857,49 @@
         </is>
       </c>
       <c r="T73" s="155" t="n">
-        <v>10.21491715724626</v>
+        <v>10.26952136764237</v>
       </c>
       <c r="U73" s="156" t="n">
-        <v>12.67310644208778</v>
+        <v>12.81375165863668</v>
       </c>
       <c r="V73" s="156" t="n">
-        <v>15.094987970368</v>
+        <v>15.35681143334573</v>
       </c>
       <c r="W73" s="156" t="n">
-        <v>17.53265173518059</v>
+        <v>17.91436548186822</v>
       </c>
       <c r="X73" s="157" t="n">
-        <v>20.19124236815906</v>
+        <v>20.71551559543687</v>
       </c>
       <c r="Y73" s="155" t="n">
-        <v>10.21491715724626</v>
+        <v>10.26952136764237</v>
       </c>
       <c r="Z73" s="156" t="n">
-        <v>12.67310644208778</v>
+        <v>12.81375165863668</v>
       </c>
       <c r="AA73" s="156" t="n">
-        <v>15.094987970368</v>
+        <v>15.35681143334573</v>
       </c>
       <c r="AB73" s="156" t="n">
-        <v>17.53265173518059</v>
+        <v>17.91436548186822</v>
       </c>
       <c r="AC73" s="157" t="n">
-        <v>20.19124236815906</v>
+        <v>20.71551559543687</v>
       </c>
       <c r="AD73" s="158" t="n">
-        <v>204.6782409735905</v>
+        <v>205.7723559391435</v>
       </c>
       <c r="AE73" s="159" t="n">
-        <v>260.5306426687525</v>
+        <v>263.4219928537459</v>
       </c>
       <c r="AF73" s="159" t="n">
-        <v>319.7497156239126</v>
+        <v>325.2957934343184</v>
       </c>
       <c r="AG73" s="159" t="n">
-        <v>378.9172421086479</v>
+        <v>387.1668738445939</v>
       </c>
       <c r="AH73" s="160" t="n">
-        <v>445.2245594222547</v>
+        <v>456.7849831136539</v>
       </c>
     </row>
     <row r="74" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -7909,49 +7909,49 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>3.22255614955571</v>
+        <v>3.282863693172597</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>3.178242892004288</v>
+        <v>3.280733732053298</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>3.583114384120006</v>
+        <v>3.745139532478443</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>4.450508379994656</v>
+        <v>4.727136117005175</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>5.896886601481767</v>
+        <v>6.354499726649944</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>3.22255614955571</v>
+        <v>3.282863693172597</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>3.178242892004288</v>
+        <v>3.280733732053298</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>3.583114384120006</v>
+        <v>3.745139532478443</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>4.450508379994656</v>
+        <v>4.727136117005175</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>5.896886601481767</v>
+        <v>6.354499726649944</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>508.838278074986</v>
+        <v>518.3607767452357</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>473.5212455639916</v>
+        <v>488.7911893310337</v>
       </c>
       <c r="O74" s="183" t="n">
-        <v>538.1549708157568</v>
+        <v>562.489845351912</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>665.3534253482376</v>
+        <v>706.7094226077015</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>893.6587861463258</v>
+        <v>963.0089394729405</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,49 +7959,49 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>3.037699497594834</v>
+        <v>3.094547597812252</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>2.985429693164918</v>
+        <v>3.081702762139446</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>3.36735770513232</v>
+        <v>3.519626534217994</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>4.186778357137026</v>
+        <v>4.447013575995512</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>5.543765441097114</v>
+        <v>5.973975482453907</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>3.037699497594834</v>
+        <v>3.094547597812252</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>2.985429693164918</v>
+        <v>3.081702762139446</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>3.36735770513232</v>
+        <v>3.519626534217994</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>4.186778357137026</v>
+        <v>4.447013575995512</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>5.543765441097114</v>
+        <v>5.973975482453907</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>508.838278074986</v>
+        <v>518.3607767452357</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>473.5212455639916</v>
+        <v>488.7911893310337</v>
       </c>
       <c r="AF74" s="189" t="n">
-        <v>538.1549708157568</v>
+        <v>562.489845351912</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>665.3534253482376</v>
+        <v>706.7094226077015</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>893.6587861463258</v>
+        <v>963.0089394729405</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,49 +8260,49 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>407.9991796458245</v>
+        <v>397.3684033167352</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>492.2486978246035</v>
+        <v>467.4914393684716</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>544.061288804637</v>
+        <v>505.3230478383018</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>585.1531932803401</v>
+        <v>533.0301224973061</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>579.3291513375884</v>
+        <v>518.2491417905404</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>407.9991796458245</v>
+        <v>397.3684033167353</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>492.2486978246035</v>
+        <v>467.4914393684716</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>544.061288804637</v>
+        <v>505.3230478383018</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>585.15319328034</v>
+        <v>533.0301224973061</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>579.3291513375883</v>
+        <v>518.2491417905404</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>28471.69447884347</v>
+        <v>27729.83951732739</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>28075.36223424783</v>
+        <v>26663.33412294043</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>28127.48764370189</v>
+        <v>26124.75483300452</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>26068.54881481979</v>
+        <v>23746.46832258388</v>
       </c>
       <c r="Q79" s="153" t="n">
-        <v>26060.96276865009</v>
+        <v>23313.29531390669</v>
       </c>
       <c r="S79" s="21" t="inlineStr">
         <is>
@@ -8310,49 +8310,49 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>412.8612179409373</v>
+        <v>402.1037569413945</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>498.1147194710693</v>
+        <v>473.0624341014024</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>550.5447499315759</v>
+        <v>511.3448736962013</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>592.1263377771166</v>
+        <v>539.3821275927095</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>586.2328919816841</v>
+        <v>524.4250051243401</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>412.8612179409373</v>
+        <v>402.1037569413945</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>498.1147194710693</v>
+        <v>473.0624341014024</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>550.5447499315759</v>
+        <v>511.3448736962013</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>592.1263377771166</v>
+        <v>539.3821275927095</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>586.2328919816841</v>
+        <v>524.4250051243401</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>28471.69447884347</v>
+        <v>27729.83951732739</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>28075.36223424783</v>
+        <v>26663.33412294043</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>28127.48764370189</v>
+        <v>26124.75483300452</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>26068.54881481979</v>
+        <v>23746.46832258388</v>
       </c>
       <c r="AH79" s="153" t="n">
-        <v>26060.96276865009</v>
+        <v>23313.29531390669</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" thickBot="1">
@@ -8362,49 +8362,49 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>1100.128962731242</v>
+        <v>1072.002775576401</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>1293.592944167114</v>
+        <v>1231.048572136083</v>
       </c>
       <c r="E80" s="156" t="n">
-        <v>1392.462090817563</v>
+        <v>1296.949563027303</v>
       </c>
       <c r="F80" s="156" t="n">
-        <v>1571.143934548078</v>
+        <v>1435.813498830977</v>
       </c>
       <c r="G80" s="157" t="n">
-        <v>1662.768847830454</v>
+        <v>1492.53112771206</v>
       </c>
       <c r="H80" s="155" t="n">
-        <v>1100.128962731241</v>
+        <v>1072.002775576401</v>
       </c>
       <c r="I80" s="156" t="n">
-        <v>1293.592944167114</v>
+        <v>1231.048572136083</v>
       </c>
       <c r="J80" s="156" t="n">
-        <v>1392.462090817563</v>
+        <v>1296.949563027303</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>1571.143934548078</v>
+        <v>1435.813498830976</v>
       </c>
       <c r="L80" s="157" t="n">
-        <v>1662.768847830453</v>
+        <v>1492.53112771206</v>
       </c>
       <c r="M80" s="158" t="n">
-        <v>26612.99924137126</v>
+        <v>25932.60428516893</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>27990.76998241881</v>
+        <v>26637.43457725192</v>
       </c>
       <c r="O80" s="159" t="n">
-        <v>30287.14377372601</v>
+        <v>28209.67130215793</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>32903.13302468607</v>
+        <v>30069.02264767003</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>35414.66909960086</v>
+        <v>31788.84189329389</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8412,49 +8412,49 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>1102.579138594785</v>
+        <v>1074.390309597729</v>
       </c>
       <c r="U80" s="156" t="n">
-        <v>1296.473997494881</v>
+        <v>1233.790328421464</v>
       </c>
       <c r="V80" s="156" t="n">
-        <v>1395.563342690208</v>
+        <v>1299.838092120905</v>
       </c>
       <c r="W80" s="156" t="n">
-        <v>1574.643141529254</v>
+        <v>1439.011301723696</v>
       </c>
       <c r="X80" s="157" t="n">
-        <v>1666.472119206468</v>
+        <v>1495.855250490929</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>1102.579138594785</v>
+        <v>1074.390309597729</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>1296.473997494881</v>
+        <v>1233.790328421464</v>
       </c>
       <c r="AA80" s="156" t="n">
-        <v>1395.563342690208</v>
+        <v>1299.838092120905</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>1574.643141529254</v>
+        <v>1439.011301723696</v>
       </c>
       <c r="AC80" s="157" t="n">
-        <v>1666.472119206468</v>
+        <v>1495.855250490929</v>
       </c>
       <c r="AD80" s="158" t="n">
-        <v>26612.99924137126</v>
+        <v>25932.60428516893</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>27990.76998241881</v>
+        <v>26637.43457725192</v>
       </c>
       <c r="AF80" s="159" t="n">
-        <v>30287.14377372601</v>
+        <v>28209.67130215793</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>32903.13302468607</v>
+        <v>30069.02264767003</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>35414.66909960086</v>
+        <v>31788.84189329389</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8464,49 +8464,49 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>586.1663633869906</v>
+        <v>571.0319402688222</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>712.6484327758649</v>
+        <v>677.4983002777803</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>795.2989800324136</v>
+        <v>739.7481185347165</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>900.4395358625893</v>
+        <v>821.709576527805</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>927.4673545100135</v>
+        <v>831.3120478848379</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>586.1663633869906</v>
+        <v>571.0319402688222</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>712.6484327758649</v>
+        <v>677.4983002777803</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>795.2989800324136</v>
+        <v>739.7481185347165</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>900.4395358625893</v>
+        <v>821.709576527805</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>927.4673545100135</v>
+        <v>831.3120478848379</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>55084.69372021472</v>
+        <v>53662.44380249632</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>56066.13221666664</v>
+        <v>53300.76870019235</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>58414.6314174279</v>
+        <v>54334.42613516246</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>58971.68183950586</v>
+        <v>53815.49097025392</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>61475.63186825095</v>
+        <v>55102.13720720058</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8514,49 +8514,49 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>591.6790432318552</v>
+        <v>576.4022864103246</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>719.228421131135</v>
+        <v>683.7537422622365</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>802.4788756246135</v>
+        <v>746.4265053916806</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>908.361658158693</v>
+        <v>828.9390278100576</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>935.6131946901389</v>
+        <v>838.6133669544026</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>591.6790432318552</v>
+        <v>576.4022864103246</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>719.228421131135</v>
+        <v>683.7537422622365</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>802.4788756246135</v>
+        <v>746.4265053916806</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>908.361658158693</v>
+        <v>828.9390278100576</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>935.6131946901389</v>
+        <v>838.6133669544026</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>55084.69372021472</v>
+        <v>53662.44380249632</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>56066.13221666664</v>
+        <v>53300.76870019235</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>58414.6314174279</v>
+        <v>54334.42613516246</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>58971.68183950586</v>
+        <v>53815.49097025392</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>61475.63186825095</v>
+        <v>55102.13720720058</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8566,49 +8566,49 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>947.0605786236081</v>
+        <v>924.6795785898768</v>
       </c>
       <c r="D82" s="156" t="n">
-        <v>1033.849289750276</v>
+        <v>986.6707468367156</v>
       </c>
       <c r="E82" s="156" t="n">
-        <v>1113.90499912244</v>
+        <v>1038.565559978139</v>
       </c>
       <c r="F82" s="156" t="n">
-        <v>1208.316346220492</v>
+        <v>1104.23465472925</v>
       </c>
       <c r="G82" s="157" t="n">
-        <v>1274.779506932834</v>
+        <v>1144.577605557737</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>947.060578623608</v>
+        <v>924.6795785898767</v>
       </c>
       <c r="I82" s="156" t="n">
-        <v>1033.849289750276</v>
+        <v>986.6707468367156</v>
       </c>
       <c r="J82" s="156" t="n">
-        <v>1113.90499912244</v>
+        <v>1038.565559978139</v>
       </c>
       <c r="K82" s="156" t="n">
-        <v>1208.316346220492</v>
+        <v>1104.23465472925</v>
       </c>
       <c r="L82" s="157" t="n">
-        <v>1274.779506932834</v>
+        <v>1144.577605557737</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>56440.48883384246</v>
+        <v>55106.68336140914</v>
       </c>
       <c r="N82" s="159" t="n">
-        <v>68103.75309619487</v>
+        <v>64995.91535825973</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>80385.61208921993</v>
+        <v>74948.69697092491</v>
       </c>
       <c r="P82" s="159" t="n">
-        <v>95866.80313029894</v>
+        <v>87609.0492243209</v>
       </c>
       <c r="Q82" s="160" t="n">
-        <v>102620.0729552573</v>
+        <v>92138.78694041265</v>
       </c>
       <c r="S82" s="32" t="inlineStr">
         <is>
@@ -8616,49 +8616,49 @@
         </is>
       </c>
       <c r="T82" s="155" t="n">
-        <v>1038.050160602331</v>
+        <v>1013.518888576184</v>
       </c>
       <c r="U82" s="156" t="n">
-        <v>1133.177164678922</v>
+        <v>1081.465906546332</v>
       </c>
       <c r="V82" s="156" t="n">
-        <v>1220.924288618642</v>
+        <v>1138.346554238556</v>
       </c>
       <c r="W82" s="156" t="n">
-        <v>1324.406279348577</v>
+        <v>1210.32485836359</v>
       </c>
       <c r="X82" s="157" t="n">
-        <v>1397.254939939913</v>
+        <v>1254.543789582905</v>
       </c>
       <c r="Y82" s="155" t="n">
-        <v>1038.050160602331</v>
+        <v>1013.518888576184</v>
       </c>
       <c r="Z82" s="156" t="n">
-        <v>1133.177164678922</v>
+        <v>1081.465906546332</v>
       </c>
       <c r="AA82" s="156" t="n">
-        <v>1220.924288618642</v>
+        <v>1138.346554238556</v>
       </c>
       <c r="AB82" s="156" t="n">
-        <v>1324.406279348577</v>
+        <v>1210.32485836359</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>1397.254939939913</v>
+        <v>1254.543789582905</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>56440.48883384246</v>
+        <v>55106.68336140914</v>
       </c>
       <c r="AE82" s="159" t="n">
-        <v>68103.75309619487</v>
+        <v>64995.91535825973</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>80385.61208921993</v>
+        <v>74948.69697092491</v>
       </c>
       <c r="AG82" s="159" t="n">
-        <v>95866.80313029894</v>
+        <v>87609.0492243209</v>
       </c>
       <c r="AH82" s="160" t="n">
-        <v>102620.0729552573</v>
+        <v>92138.78694041265</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" thickTop="1">
@@ -8668,49 +8668,49 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>726.2175229297255</v>
+        <v>708.2709419633778</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>859.0284422615587</v>
+        <v>818.3966343803496</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>953.1969568453584</v>
+        <v>887.8390729212526</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>1069.095711027092</v>
+        <v>976.477969191467</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>1117.943115606288</v>
+        <v>1003.115698021307</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>726.2175229297255</v>
+        <v>708.2709419633778</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>859.0284422615587</v>
+        <v>818.3966343803496</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>953.1969568453584</v>
+        <v>887.8390729212526</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>1069.095711027092</v>
+        <v>976.477969191467</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>1117.943115606288</v>
+        <v>1003.115698021307</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>111525.1825540572</v>
+        <v>108769.1271639055</v>
       </c>
       <c r="N83" s="165" t="n">
-        <v>124169.8853128615</v>
+        <v>118296.6840584521</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>138800.2435066478</v>
+        <v>129283.1231060874</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>154838.4849698048</v>
+        <v>141424.5401945748</v>
       </c>
       <c r="Q83" s="166" t="n">
-        <v>164095.7048235083</v>
+        <v>147240.9241476132</v>
       </c>
       <c r="S83" s="42" t="inlineStr">
         <is>
@@ -8718,49 +8718,49 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>756.2537599883484</v>
+        <v>737.564911391054</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>899.4363812986289</v>
+        <v>856.8932890698291</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>1001.208550965399</v>
+        <v>932.5586546476599</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>1127.691872325746</v>
+        <v>1029.997836493484</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>1179.269456006546</v>
+        <v>1058.143019088832</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>756.2537599883484</v>
+        <v>737.564911391054</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>899.4363812986289</v>
+        <v>856.8932890698291</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>1001.208550965399</v>
+        <v>932.5586546476599</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>1127.691872325746</v>
+        <v>1029.997836493484</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>1179.269456006546</v>
+        <v>1058.143019088832</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>111525.1825540572</v>
+        <v>108769.1271639055</v>
       </c>
       <c r="AE83" s="165" t="n">
-        <v>124169.8853128615</v>
+        <v>118296.6840584521</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>138800.2435066478</v>
+        <v>129283.1231060874</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>154838.4849698048</v>
+        <v>141424.5401945748</v>
       </c>
       <c r="AH83" s="166" t="n">
-        <v>164095.7048235083</v>
+        <v>147240.9241476132</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" thickBot="1">
@@ -8770,49 +8770,49 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>367.9492727259788</v>
+        <v>358.929123670983</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>410.9473790975439</v>
+        <v>391.4328203471416</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>457.0923312475084</v>
+        <v>425.3285827505294</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>500.9150699099199</v>
+        <v>459.2916873538657</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>547.4100692171794</v>
+        <v>495.5685616056477</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>367.9492727259787</v>
+        <v>358.9291236709831</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>410.9473790975439</v>
+        <v>391.4328203471416</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>457.0923312475084</v>
+        <v>425.3285827505294</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>500.9150699099199</v>
+        <v>459.2916873538656</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>547.4100692171793</v>
+        <v>495.5685616056477</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>1592.860731220918</v>
+        <v>1553.812301764822</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>1825.218966490081</v>
+        <v>1738.545235093768</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>2091.868405118662</v>
+        <v>1946.502628082717</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>2338.912036624588</v>
+        <v>2144.560865511105</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>2607.845644359086</v>
+        <v>2360.874210283941</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>79.49521324326703</v>
+        <v>77.54641560792845</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>88.78492758280271</v>
+        <v>84.5688192108022</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>98.75451601026415</v>
+        <v>91.891977754744</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>108.2223916472049</v>
+        <v>99.22968553941541</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>118.2676075469215</v>
+        <v>107.0672818283807</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>79.49521324326703</v>
+        <v>77.54641560792845</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>88.78492758280271</v>
+        <v>84.5688192108022</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>98.75451601026415</v>
+        <v>91.891977754744</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>108.2223916472049</v>
+        <v>99.22968553941541</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>118.2676075469215</v>
+        <v>107.0672818283807</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>1592.860731220918</v>
+        <v>1553.812301764822</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>1825.218966490081</v>
+        <v>1738.545235093768</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>2091.868405118662</v>
+        <v>1946.502628082717</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>2338.912036624588</v>
+        <v>2144.560865511105</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>2607.845644359086</v>
+        <v>2360.874210283941</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,49 +8872,49 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>716.3950939260161</v>
+        <v>698.6932436709603</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>845.6707029612517</v>
+        <v>805.6684211453423</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>938.0802560177989</v>
+        <v>873.7460120047308</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>1051.349998170884</v>
+        <v>960.3249386471419</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>1100.008133319518</v>
+        <v>987.1607082815765</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>716.3950939260161</v>
+        <v>698.6932436709603</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>845.6707029612517</v>
+        <v>805.6684211453423</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>938.0802560177989</v>
+        <v>873.7460120047308</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>1051.349998170884</v>
+        <v>960.3249386471419</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>1100.008133319518</v>
+        <v>987.1607082815765</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>113118.0432852781</v>
+        <v>110322.9394656703</v>
       </c>
       <c r="N85" s="183" t="n">
-        <v>125995.1042793516</v>
+        <v>120035.2292935459</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>140892.1119117665</v>
+        <v>131229.6257341701</v>
       </c>
       <c r="P85" s="183" t="n">
-        <v>157177.3970064294</v>
+        <v>143569.1010600859</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>166703.5504678674</v>
+        <v>149601.7983578972</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8922,49 +8922,49 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>675.300263487571</v>
+        <v>658.6138508602237</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>794.3667344027411</v>
+        <v>756.7912551251788</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>881.5938983510378</v>
+        <v>821.1335309004819</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>989.0486754062005</v>
+        <v>903.4176156189204</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>1034.136738001735</v>
+        <v>928.0469151306393</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>675.300263487571</v>
+        <v>658.6138508602237</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>794.3667344027411</v>
+        <v>756.7912551251788</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>881.5938983510378</v>
+        <v>821.1335309004819</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>989.0486754062005</v>
+        <v>903.4176156189204</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>1034.136738001735</v>
+        <v>928.0469151306393</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>113118.0432852781</v>
+        <v>110322.9394656703</v>
       </c>
       <c r="AE85" s="189" t="n">
-        <v>125995.1042793516</v>
+        <v>120035.2292935459</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>140892.1119117665</v>
+        <v>131229.6257341701</v>
       </c>
       <c r="AG85" s="189" t="n">
-        <v>157177.3970064294</v>
+        <v>143569.1010600859</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>166703.5504678674</v>
+        <v>149601.7983578972</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9880,7 +9880,7 @@
         <v>4.669278640479308</v>
       </c>
       <c r="G95" s="81" t="n">
-        <v>4.763970907748228</v>
+        <v>4.763970907748229</v>
       </c>
       <c r="H95" s="79" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
         <v>4.669278640479308</v>
       </c>
       <c r="Q95" s="81" t="n">
-        <v>4.763970907748228</v>
+        <v>4.763970907748229</v>
       </c>
       <c r="S95" s="32" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>20.0371904953136</v>
       </c>
       <c r="U95" s="80" t="n">
-        <v>20.55775699977727</v>
+        <v>20.55775699977728</v>
       </c>
       <c r="V95" s="80" t="n">
         <v>21.18250880700222</v>
@@ -9930,7 +9930,7 @@
         <v>21.61208970736137</v>
       </c>
       <c r="X95" s="81" t="n">
-        <v>22.05037963014894</v>
+        <v>22.05037963014895</v>
       </c>
       <c r="Y95" s="79" t="n">
         <v>0</v>
@@ -9951,7 +9951,7 @@
         <v>20.0371904953136</v>
       </c>
       <c r="AE95" s="80" t="n">
-        <v>20.55775699977727</v>
+        <v>20.55775699977728</v>
       </c>
       <c r="AF95" s="80" t="n">
         <v>21.18250880700222</v>
@@ -9960,7 +9960,7 @@
         <v>21.61208970736137</v>
       </c>
       <c r="AH95" s="81" t="n">
-        <v>22.05037963014894</v>
+        <v>22.05037963014895</v>
       </c>
       <c r="AJ95" s="120" t="n">
         <v>138.8571428571429</v>
